--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4C2837-E716-4950-80C4-2FA8EF66C3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB955357FD0AFC93B1776B2B13C70D860FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64E89BB8-53E7-4B47-9D19-C55478E361F2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 09-09-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 14-09-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -695,7 +695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -729,7 +729,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -788,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -802,7 +802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -830,7 +830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -844,7 +844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -858,7 +858,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -934,7 +934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -962,7 +962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -976,7 +976,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -990,7 +990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>94</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB955357FD0AFC93B1776B2B13C70D860FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64E89BB8-53E7-4B47-9D19-C55478E361F2}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB955357FD0AFC93B44D635ACB671D860FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{676C2D6A-C2C2-48E8-802E-AB4A7C7AFD68}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB955357FD0AFC93B44D635ACB671D860FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{676C2D6A-C2C2-48E8-802E-AB4A7C7AFD68}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7F4F1D-0925-4D59-B685-A4223DDF597C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -695,7 +695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -729,7 +729,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -788,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -802,7 +802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -830,7 +830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -844,7 +844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -858,7 +858,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -934,7 +934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -962,7 +962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -976,7 +976,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -990,7 +990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>94</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7F4F1D-0925-4D59-B685-A4223DDF597C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E59669-9D9B-46F8-9F78-3726FF8601AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 14-09-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 17-09-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -43,7 +43,7 @@
     <t>Vena _SPL_ (Vena)</t>
   </si>
   <si>
-    <t>Xmedicus _SPL_ (Xmedicus Systems)</t>
+    <t>Xmedicus _SPL_ (XMedicus Systems)</t>
   </si>
   <si>
     <t>Binær dokumenttransport</t>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -695,7 +695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -712,7 +712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -729,7 +729,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -788,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -802,7 +802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -830,7 +830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -844,7 +844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -858,7 +858,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -934,7 +934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -959,10 +959,10 @@
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -976,7 +976,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -990,7 +990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>94</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E59669-9D9B-46F8-9F78-3726FF8601AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2631D626-CEF8-430F-ADA0-2EE29687AEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2631D626-CEF8-430F-ADA0-2EE29687AEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FDDDFAE31DC83B10BE7088CC71D860DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2198049-1279-46D9-8E7F-485DD25CE640}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 17-09-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 21-09-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -58,13 +58,13 @@
     <t>Ikke Godkendt</t>
   </si>
   <si>
+    <t>Godkendt</t>
+  </si>
+  <si>
     <t>Negativ VANS kvittering</t>
   </si>
   <si>
     <t>CTL01 (C0130Q)</t>
-  </si>
-  <si>
-    <t>Godkendt</t>
   </si>
   <si>
     <t>Negativ kvittering</t>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -692,27 +692,27 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -723,13 +723,13 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -740,13 +740,13 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -788,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -799,10 +799,10 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -827,10 +827,10 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -844,7 +844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -855,10 +855,10 @@
         <v>9</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -897,10 +897,10 @@
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -931,10 +931,10 @@
         <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -959,10 +959,10 @@
         <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -973,10 +973,10 @@
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -987,10 +987,10 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1004,13 +1004,13 @@
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1021,10 +1021,10 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1035,10 +1035,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1049,13 +1049,13 @@
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G26" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1066,10 +1066,10 @@
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1094,10 +1094,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1108,10 +1108,10 @@
         <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1178,13 +1178,13 @@
         <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G35" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1209,13 +1209,13 @@
         <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1226,13 +1226,13 @@
         <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1243,10 +1243,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1257,10 +1257,10 @@
         <v>74</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1271,13 +1271,13 @@
         <v>74</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G41" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1288,13 +1288,13 @@
         <v>74</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -1305,13 +1305,13 @@
         <v>74</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G43" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1322,10 +1322,10 @@
         <v>74</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1336,16 +1336,16 @@
         <v>74</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1373,10 +1373,10 @@
         <v>10</v>
       </c>
       <c r="G47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1415,10 +1415,10 @@
         <v>74</v>
       </c>
       <c r="G50" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1429,10 +1429,10 @@
         <v>74</v>
       </c>
       <c r="G51" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1443,10 +1443,10 @@
         <v>74</v>
       </c>
       <c r="G52" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1527,13 +1527,13 @@
         <v>74</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G58" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1544,10 +1544,10 @@
         <v>74</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>94</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FDDDFAE31DC83B10BE7088CC71D860DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2198049-1279-46D9-8E7F-485DD25CE640}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3ACFFC8-E6EC-4BDA-828F-788EC07BD4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -695,7 +695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -712,7 +712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -746,7 +746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -788,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -802,7 +802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -830,7 +830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -844,7 +844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -858,7 +858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -962,7 +962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -976,7 +976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -990,7 +990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1150,10 +1150,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>94</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3ACFFC8-E6EC-4BDA-828F-788EC07BD4C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3785DF2-0326-4A8B-8CD8-B58E3E033A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 21-09-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 22-09-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3785DF2-0326-4A8B-8CD8-B58E3E033A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EA1580-4BC3-4951-8438-7A0BD066701B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 22-09-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 23-09-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EA1580-4BC3-4951-8438-7A0BD066701B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB906F5F9DFC5C83B135676946A71D860AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{631B7EF5-EAD5-40D7-BEA0-3F803A12E21F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 23-09-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 24-09-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -43,10 +43,10 @@
     <t>Vena _SPL_ (Vena)</t>
   </si>
   <si>
-    <t>Xmedicus _SPL_ (XMedicus Systems)</t>
-  </si>
-  <si>
-    <t>Binær dokumenttransport</t>
+    <t>XMedicus _SPL_ (XMedicus Systems)</t>
+  </si>
+  <si>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -695,7 +695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -712,7 +712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -746,7 +746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -788,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -802,7 +802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -830,7 +830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -841,10 +841,10 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -858,7 +858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -962,7 +962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -976,7 +976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -990,7 +990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>94</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB906F5F9DFC5C83B135676946A71D860AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{631B7EF5-EAD5-40D7-BEA0-3F803A12E21F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94502747-8754-4023-BB02-11C0FEFCB1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 24-09-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 28-09-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -695,7 +695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -712,7 +712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -746,7 +746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -788,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -802,7 +802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -830,7 +830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -844,7 +844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -858,7 +858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -962,7 +962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -976,7 +976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -990,7 +990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>94</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94502747-8754-4023-BB02-11C0FEFCB1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB906F5F9DFC5C83B771631AF2C70D860AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F85A082-4354-447F-AD1F-1D649F0717B7}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 28-09-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 02-10-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -695,7 +695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -712,7 +712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -746,7 +746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -788,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -802,7 +802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -830,7 +830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -844,7 +844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -858,7 +858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -962,7 +962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -976,7 +976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -990,7 +990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>94</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3785DF2-0326-4A8B-8CD8-B58E3E033A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D725516A-91D3-49EF-8F19-3B257397974A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 22-09-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 07-10-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -43,10 +43,10 @@
     <t>Vena _SPL_ (Vena)</t>
   </si>
   <si>
-    <t>Xmedicus _SPL_ (XMedicus Systems)</t>
-  </si>
-  <si>
-    <t>Binær dokumenttransport</t>
+    <t>XMedicus _SPL_ (XMedicus Systems)</t>
+  </si>
+  <si>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>
@@ -841,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB906F5F9DFC5C83B771631AF2C70D860AD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F85A082-4354-447F-AD1F-1D649F0717B7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75328FE-9226-4373-8227-1BF08F9454F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 02-10-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 07-10-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -695,7 +695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -712,7 +712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -729,7 +729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -746,7 +746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -788,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -802,7 +802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -830,7 +830,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -844,7 +844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -858,7 +858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -872,7 +872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -886,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -900,7 +900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -934,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -948,7 +948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -962,7 +962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -976,7 +976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -990,7 +990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>68</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>28</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>94</v>
       </c>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75328FE-9226-4373-8227-1BF08F9454F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB906F5F9DFC5C83B39FEB7A34271D860A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{061E1CA5-7673-4739-BE7E-5B9E35CAC099}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 07-10-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 08-10-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB906F5F9DFC5C83B39FEB7A34271D860A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{061E1CA5-7673-4739-BE7E-5B9E35CAC099}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413E885F-41B3-43C0-87CA-CD8AF59274F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 08-10-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 09-10-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413E885F-41B3-43C0-87CA-CD8AF59274F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4B625C-130D-47E5-8796-91F18256936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Speciallægesystemer_excel.XLSX
+++ b/html/Speciallægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4B625C-130D-47E5-8796-91F18256936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB906F5F9DFC5C83BD83E72849E71D860A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ABCAFC1-6D87-43F1-B3FB-047FA3312301}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Speciallægesystemer">'Opdateret d. 09-10-2026'!$A$1:$G$61</definedName>
+    <definedName name="Speciallægesystemer">'Opdateret d. 23-10-2026'!$A$1:$G$61</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
